--- a/Knowledge/Model Outputs/MNST/MNST_disclosures.xlsx
+++ b/Knowledge/Model Outputs/MNST/MNST_disclosures.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;--&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;--&quot;"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.00;($#,##0.00);&quot;--&quot;"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -89,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +103,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2654,7 +2656,7 @@
         <t>ShareBasedCompensation @ FY2020; raw=58,200,000</t>
       </text>
     </comment>
-    <comment ref="J67" authorId="0" shapeId="0">
+    <comment ref="K67" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensation @ FY2021; raw=60,600,000</t>
       </text>
@@ -2669,7 +2671,7 @@
         <t>ShareBasedCompensation @ FY2023; raw=57,300,000</t>
       </text>
     </comment>
-    <comment ref="Y67" authorId="0" shapeId="0">
+    <comment ref="Z67" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensation @ FY2024; raw=78,400,000</t>
       </text>
@@ -2679,7 +2681,7 @@
         <t>AllocatedShareBasedCompensationExpense @ FY2023; raw=57,300,000</t>
       </text>
     </comment>
-    <comment ref="Y68" authorId="0" shapeId="0">
+    <comment ref="Z68" authorId="0" shapeId="0">
       <text>
         <t>AllocatedShareBasedCompensationExpense @ FY2024; raw=78,400,000</t>
       </text>
@@ -2699,7 +2701,7 @@
         <t>ShareBasedCompensation @ FY2020; raw=9,400,000</t>
       </text>
     </comment>
-    <comment ref="J69" authorId="0" shapeId="0">
+    <comment ref="K69" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensation @ FY2021; raw=8,300,000</t>
       </text>
@@ -2714,7 +2716,7 @@
         <t>ShareBasedCompensation @ FY2023; raw=10,300,000</t>
       </text>
     </comment>
-    <comment ref="Y69" authorId="0" shapeId="0">
+    <comment ref="Z69" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensation @ FY2024; raw=12,500,000</t>
       </text>
@@ -2729,7 +2731,7 @@
         <t>ShareBasedCompensation @ FY2020; raw=2,700,000</t>
       </text>
     </comment>
-    <comment ref="J70" authorId="0" shapeId="0">
+    <comment ref="K70" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensation @ FY2021; raw=1,600,000</t>
       </text>
@@ -2744,7 +2746,7 @@
         <t>ShareBasedCompensation @ FY2023; raw=1,200,000</t>
       </text>
     </comment>
-    <comment ref="Y70" authorId="0" shapeId="0">
+    <comment ref="Z70" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensation @ FY2024; raw=100,000</t>
       </text>
@@ -2819,7 +2821,7 @@
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ Q3 2024; raw=48</t>
       </text>
     </comment>
-    <comment ref="Z73" authorId="0" shapeId="0">
+    <comment ref="Y73" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ Q4 2024; raw=49</t>
       </text>
@@ -2886,14 +2888,14 @@
     </comment>
     <comment ref="J74" authorId="0" shapeId="0">
       <text>
+        <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ Q4 2021; raw=90</t>
+      </text>
+    </comment>
+    <comment ref="K74" authorId="0" shapeId="0">
+      <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ FY2021; raw=89</t>
       </text>
     </comment>
-    <comment ref="K74" authorId="0" shapeId="0">
-      <text>
-        <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ Q4 2021; raw=90</t>
-      </text>
-    </comment>
     <comment ref="L74" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ Q1 2022; raw=72</t>
@@ -2919,7 +2921,7 @@
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ Q4 2022; raw=90</t>
       </text>
     </comment>
-    <comment ref="J75" authorId="0" shapeId="0">
+    <comment ref="K75" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ FY2021; raw=45</t>
       </text>
@@ -2959,7 +2961,7 @@
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ Q3 2024; raw=48</t>
       </text>
     </comment>
-    <comment ref="Y75" authorId="0" shapeId="0">
+    <comment ref="Z75" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ FY2024; raw=59</t>
       </text>
@@ -3049,7 +3051,7 @@
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriod @ Q3 2024; raw=32,000</t>
       </text>
     </comment>
-    <comment ref="Z78" authorId="0" shapeId="0">
+    <comment ref="Y78" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriod @ Q4 2024; raw=2,000</t>
       </text>
@@ -3089,7 +3091,7 @@
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriod @ Q3 2021; raw=1,000</t>
       </text>
     </comment>
-    <comment ref="K79" authorId="0" shapeId="0">
+    <comment ref="J79" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriod @ Q4 2021; raw=1,000</t>
       </text>
@@ -3139,7 +3141,7 @@
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsVestedInPeriod @ Q1 2024; raw=821,000</t>
       </text>
     </comment>
-    <comment ref="Y82" authorId="0" shapeId="0">
+    <comment ref="Z82" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsVestedInPeriod @ FY2024; raw=829,000</t>
       </text>
@@ -3154,7 +3156,7 @@
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsVestedInPeriod @ FY2025; raw=635,000</t>
       </text>
     </comment>
-    <comment ref="J83" authorId="0" shapeId="0">
+    <comment ref="K83" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsVestedInPeriod @ FY2021; raw=344,000</t>
       </text>
@@ -6298,7 +6300,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>25. CUSTOMER CONCENTRATION (% OF REVENUE)  (% of revenue)</t>
+          <t>25. CUSTOMER CONCENTRATION (% OF REVENUE)  (% values)</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6827,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4. DEBT SCHEDULE  ($ in thousands)</t>
+          <t>4. DEBT SCHEDULE  (mixed: $ in thousands, % / counts as labeled)</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6887,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>5. STOCK-BASED COMPENSATION BY AWARD TYPE  ($ in thousands)</t>
+          <t>5. STOCK-BASED COMPENSATION BY AWARD TYPE  (mixed: $ in thousands, % / counts as labeled)</t>
         </is>
       </c>
     </row>
@@ -6937,14 +6939,14 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
+          <t>Q4 2021</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>Q4 2021</t>
-        </is>
-      </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
           <t>Q1 2022</t>
@@ -7012,12 +7014,12 @@
       </c>
       <c r="Y65" s="5" t="inlineStr">
         <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="Z65" s="5" t="inlineStr">
+        <is>
           <t>FY2024</t>
-        </is>
-      </c>
-      <c r="Z65" s="5" t="inlineStr">
-        <is>
-          <t>Q4 2024</t>
         </is>
       </c>
       <c r="AA65" s="5" t="inlineStr">
@@ -7065,7 +7067,7 @@
       <c r="F67" s="8" t="n">
         <v>58200</v>
       </c>
-      <c r="J67" s="8" t="n">
+      <c r="K67" s="8" t="n">
         <v>60600</v>
       </c>
       <c r="O67" s="8" t="n">
@@ -7074,7 +7076,7 @@
       <c r="U67" s="8" t="n">
         <v>57300</v>
       </c>
-      <c r="Y67" s="8" t="n">
+      <c r="Z67" s="8" t="n">
         <v>78400</v>
       </c>
     </row>
@@ -7087,7 +7089,7 @@
       <c r="U68" s="8" t="n">
         <v>57300</v>
       </c>
-      <c r="Y68" s="8" t="n">
+      <c r="Z68" s="8" t="n">
         <v>78400</v>
       </c>
       <c r="AE68" s="8" t="n">
@@ -7106,7 +7108,7 @@
       <c r="F69" s="8" t="n">
         <v>9400</v>
       </c>
-      <c r="J69" s="8" t="n">
+      <c r="K69" s="8" t="n">
         <v>8300.000000000002</v>
       </c>
       <c r="O69" s="8" t="n">
@@ -7115,7 +7117,7 @@
       <c r="U69" s="8" t="n">
         <v>10300</v>
       </c>
-      <c r="Y69" s="8" t="n">
+      <c r="Z69" s="8" t="n">
         <v>12500</v>
       </c>
       <c r="AE69" s="8" t="n">
@@ -7131,7 +7133,7 @@
       <c r="F70" s="8" t="n">
         <v>2700</v>
       </c>
-      <c r="J70" s="8" t="n">
+      <c r="K70" s="8" t="n">
         <v>1600</v>
       </c>
       <c r="O70" s="8" t="n">
@@ -7140,7 +7142,7 @@
       <c r="U70" s="8" t="n">
         <v>1200</v>
       </c>
-      <c r="Y70" s="8" t="n">
+      <c r="Z70" s="8" t="n">
         <v>100</v>
       </c>
       <c r="AE70" s="8" t="n">
@@ -7150,7 +7152,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Wtd Avg Grant FV $</t>
+          <t>Wtd Avg Grant FV (per share)</t>
         </is>
       </c>
     </row>
@@ -7160,59 +7162,59 @@
           <t xml:space="preserve">  RSUs + PSUs</t>
         </is>
       </c>
-      <c r="G73" s="8" t="n">
-        <v>0.08628</v>
-      </c>
-      <c r="H73" s="8" t="n">
-        <v>0.09214</v>
-      </c>
-      <c r="I73" s="8" t="n">
-        <v>0.08984</v>
-      </c>
-      <c r="L73" s="8" t="n">
-        <v>0.07188</v>
-      </c>
-      <c r="M73" s="8" t="n">
-        <v>0.08752</v>
-      </c>
-      <c r="N73" s="8" t="n">
-        <v>0.09517</v>
-      </c>
-      <c r="Q73" s="8" t="n">
-        <v>0.04849000000000001</v>
-      </c>
-      <c r="R73" s="8" t="n">
-        <v>0.0597</v>
-      </c>
-      <c r="S73" s="8" t="n">
-        <v>0.05638</v>
-      </c>
-      <c r="T73" s="8" t="n">
-        <v>0.05199</v>
-      </c>
-      <c r="V73" s="8" t="n">
-        <v>0.05704</v>
-      </c>
-      <c r="W73" s="8" t="n">
-        <v>0.04912</v>
-      </c>
-      <c r="X73" s="8" t="n">
-        <v>0.0484</v>
-      </c>
-      <c r="Z73" s="8" t="n">
-        <v>0.04924</v>
-      </c>
-      <c r="AA73" s="8" t="n">
-        <v>0.05508</v>
-      </c>
-      <c r="AB73" s="8" t="n">
-        <v>0.06268</v>
-      </c>
-      <c r="AC73" s="8" t="n">
-        <v>0.06159000000000001</v>
-      </c>
-      <c r="AD73" s="8" t="n">
-        <v>0.06672</v>
+      <c r="G73" s="10" t="n">
+        <v>86.28</v>
+      </c>
+      <c r="H73" s="10" t="n">
+        <v>92.14</v>
+      </c>
+      <c r="I73" s="10" t="n">
+        <v>89.84</v>
+      </c>
+      <c r="L73" s="10" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="M73" s="10" t="n">
+        <v>87.52</v>
+      </c>
+      <c r="N73" s="10" t="n">
+        <v>95.17</v>
+      </c>
+      <c r="Q73" s="10" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="R73" s="10" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="S73" s="10" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="T73" s="10" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="V73" s="10" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="W73" s="10" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="X73" s="10" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="Y73" s="10" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="AA73" s="10" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="AB73" s="10" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="AC73" s="10" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="AD73" s="10" t="n">
+        <v>66.72</v>
       </c>
     </row>
     <row r="74">
@@ -7221,50 +7223,50 @@
           <t xml:space="preserve">  RSUs</t>
         </is>
       </c>
-      <c r="B74" s="8" t="n">
-        <v>0.05979</v>
-      </c>
-      <c r="C74" s="8" t="n">
-        <v>0.06239</v>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>0.07171999999999999</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0.07176</v>
-      </c>
-      <c r="F74" s="8" t="n">
-        <v>0.06297</v>
-      </c>
-      <c r="G74" s="8" t="n">
-        <v>0.08628</v>
-      </c>
-      <c r="H74" s="8" t="n">
-        <v>0.09214</v>
-      </c>
-      <c r="I74" s="8" t="n">
-        <v>0.08984</v>
-      </c>
-      <c r="J74" s="8" t="n">
-        <v>0.08912</v>
-      </c>
-      <c r="K74" s="8" t="n">
-        <v>0.08995</v>
-      </c>
-      <c r="L74" s="8" t="n">
-        <v>0.07188</v>
-      </c>
-      <c r="M74" s="8" t="n">
-        <v>0.08752</v>
-      </c>
-      <c r="N74" s="8" t="n">
-        <v>0.09517</v>
-      </c>
-      <c r="O74" s="8" t="n">
-        <v>0.07426000000000001</v>
-      </c>
-      <c r="P74" s="8" t="n">
-        <v>0.09029000000000001</v>
+      <c r="B74" s="10" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="C74" s="10" t="n">
+        <v>62.39</v>
+      </c>
+      <c r="D74" s="10" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>86.28</v>
+      </c>
+      <c r="H74" s="10" t="n">
+        <v>92.14</v>
+      </c>
+      <c r="I74" s="10" t="n">
+        <v>89.84</v>
+      </c>
+      <c r="J74" s="10" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="K74" s="10" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="L74" s="10" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="M74" s="10" t="n">
+        <v>87.52</v>
+      </c>
+      <c r="N74" s="10" t="n">
+        <v>95.17</v>
+      </c>
+      <c r="O74" s="10" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="P74" s="10" t="n">
+        <v>90.29000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -7273,44 +7275,44 @@
           <t xml:space="preserve">  RSUs and/or PSUs</t>
         </is>
       </c>
-      <c r="J75" s="8" t="n">
-        <v>0.04456</v>
-      </c>
-      <c r="O75" s="8" t="n">
-        <v>0.03713</v>
-      </c>
-      <c r="R75" s="8" t="n">
-        <v>0.05917</v>
-      </c>
-      <c r="S75" s="8" t="n">
-        <v>0.05638</v>
-      </c>
-      <c r="U75" s="8" t="n">
-        <v>0.05124</v>
-      </c>
-      <c r="V75" s="8" t="n">
-        <v>0.06027</v>
-      </c>
-      <c r="W75" s="8" t="n">
-        <v>0.04912</v>
-      </c>
-      <c r="X75" s="8" t="n">
-        <v>0.0484</v>
-      </c>
-      <c r="Y75" s="8" t="n">
-        <v>0.05877</v>
-      </c>
-      <c r="AA75" s="8" t="n">
-        <v>0.05508</v>
-      </c>
-      <c r="AB75" s="8" t="n">
-        <v>0.06268</v>
-      </c>
-      <c r="AC75" s="8" t="n">
-        <v>0.06159000000000001</v>
-      </c>
-      <c r="AE75" s="8" t="n">
-        <v>0.0554</v>
+      <c r="K75" s="10" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="O75" s="10" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="R75" s="10" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="S75" s="10" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="U75" s="10" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="V75" s="10" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="W75" s="10" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="X75" s="10" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="Z75" s="10" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="AA75" s="10" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="AB75" s="10" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="AC75" s="10" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="AE75" s="10" t="n">
+        <v>55.4</v>
       </c>
     </row>
     <row r="77">
@@ -7327,58 +7329,58 @@
         </is>
       </c>
       <c r="G78" s="8" t="n">
-        <v>304</v>
+        <v>304000</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>14</v>
+        <v>14000</v>
       </c>
       <c r="I78" s="8" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="L78" s="8" t="n">
-        <v>484</v>
+        <v>484000</v>
       </c>
       <c r="M78" s="8" t="n">
-        <v>15</v>
+        <v>15000</v>
       </c>
       <c r="N78" s="8" t="n">
-        <v>6</v>
+        <v>6000</v>
       </c>
       <c r="Q78" s="8" t="n">
-        <v>523</v>
+        <v>523000</v>
       </c>
       <c r="R78" s="8" t="n">
-        <v>22</v>
+        <v>22000</v>
       </c>
       <c r="S78" s="8" t="n">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="T78" s="8" t="n">
-        <v>8</v>
+        <v>8000</v>
       </c>
       <c r="V78" s="8" t="n">
-        <v>502</v>
+        <v>502000</v>
       </c>
       <c r="W78" s="8" t="n">
-        <v>27</v>
+        <v>27000</v>
       </c>
       <c r="X78" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z78" s="8" t="n">
-        <v>2</v>
+        <v>32000</v>
+      </c>
+      <c r="Y78" s="8" t="n">
+        <v>2000</v>
       </c>
       <c r="AA78" s="8" t="n">
-        <v>1017</v>
+        <v>1017000</v>
       </c>
       <c r="AB78" s="8" t="n">
-        <v>33</v>
+        <v>33000</v>
       </c>
       <c r="AC78" s="8" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="AD78" s="8" t="n">
-        <v>7</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="79">
@@ -7388,28 +7390,28 @@
         </is>
       </c>
       <c r="G79" s="8" t="n">
-        <v>304</v>
+        <v>304000</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>14</v>
+        <v>14000</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" s="8" t="n">
-        <v>1</v>
+        <v>1000</v>
+      </c>
+      <c r="J79" s="8" t="n">
+        <v>1000</v>
       </c>
       <c r="L79" s="8" t="n">
-        <v>484</v>
+        <v>484000</v>
       </c>
       <c r="M79" s="8" t="n">
-        <v>15</v>
+        <v>15000</v>
       </c>
       <c r="N79" s="8" t="n">
-        <v>6</v>
+        <v>6000</v>
       </c>
       <c r="P79" s="8" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="81">
@@ -7426,28 +7428,28 @@
         </is>
       </c>
       <c r="G82" s="8" t="n">
-        <v>335</v>
+        <v>335000</v>
       </c>
       <c r="L82" s="8" t="n">
-        <v>371</v>
+        <v>371000</v>
       </c>
       <c r="Q82" s="8" t="n">
-        <v>576</v>
+        <v>576000</v>
       </c>
       <c r="U82" s="8" t="n">
-        <v>595</v>
+        <v>595000</v>
       </c>
       <c r="V82" s="8" t="n">
-        <v>821</v>
-      </c>
-      <c r="Y82" s="8" t="n">
-        <v>829</v>
+        <v>821000</v>
+      </c>
+      <c r="Z82" s="8" t="n">
+        <v>829000</v>
       </c>
       <c r="AA82" s="8" t="n">
-        <v>613</v>
+        <v>613000</v>
       </c>
       <c r="AE82" s="8" t="n">
-        <v>635</v>
+        <v>635000</v>
       </c>
     </row>
     <row r="83">
@@ -7456,17 +7458,17 @@
           <t xml:space="preserve">  RSUs</t>
         </is>
       </c>
-      <c r="J83" s="8" t="n">
-        <v>344</v>
+      <c r="K83" s="8" t="n">
+        <v>344000</v>
       </c>
       <c r="O83" s="8" t="n">
-        <v>389</v>
+        <v>389000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>7. PP&amp;E BY CLASS  ($ in thousands)</t>
+          <t>7. PP&amp;E BY CLASS  (mixed: $ in thousands, % / counts as labeled)</t>
         </is>
       </c>
     </row>

--- a/Knowledge/Model Outputs/MNST/MNST_disclosures.xlsx
+++ b/Knowledge/Model Outputs/MNST/MNST_disclosures.xlsx
@@ -2661,7 +2661,7 @@
         <t>ShareBasedCompensation @ FY2021; raw=60,600,000</t>
       </text>
     </comment>
-    <comment ref="O67" authorId="0" shapeId="0">
+    <comment ref="P67" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensation @ FY2022; raw=54,000,000</t>
       </text>
@@ -2706,7 +2706,7 @@
         <t>ShareBasedCompensation @ FY2021; raw=8,300,000</t>
       </text>
     </comment>
-    <comment ref="O69" authorId="0" shapeId="0">
+    <comment ref="P69" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensation @ FY2022; raw=9,400,000</t>
       </text>
@@ -2736,7 +2736,7 @@
         <t>ShareBasedCompensation @ FY2021; raw=1,600,000</t>
       </text>
     </comment>
-    <comment ref="O70" authorId="0" shapeId="0">
+    <comment ref="P70" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensation @ FY2022; raw=700,000</t>
       </text>
@@ -2913,20 +2913,20 @@
     </comment>
     <comment ref="O74" authorId="0" shapeId="0">
       <text>
+        <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ Q4 2022; raw=90</t>
+      </text>
+    </comment>
+    <comment ref="P74" authorId="0" shapeId="0">
+      <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ FY2022; raw=74</t>
       </text>
     </comment>
-    <comment ref="P74" authorId="0" shapeId="0">
-      <text>
-        <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ Q4 2022; raw=90</t>
-      </text>
-    </comment>
     <comment ref="K75" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ FY2021; raw=45</t>
       </text>
     </comment>
-    <comment ref="O75" authorId="0" shapeId="0">
+    <comment ref="P75" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriodWeightedAverageGrantDateFairValue @ FY2022; raw=37</t>
       </text>
@@ -3111,7 +3111,7 @@
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriod @ Q3 2022; raw=6,000</t>
       </text>
     </comment>
-    <comment ref="P79" authorId="0" shapeId="0">
+    <comment ref="O79" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsGrantsInPeriod @ Q4 2022; raw=1,000</t>
       </text>
@@ -3161,7 +3161,7 @@
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsVestedInPeriod @ FY2021; raw=344,000</t>
       </text>
     </comment>
-    <comment ref="O83" authorId="0" shapeId="0">
+    <comment ref="P83" authorId="0" shapeId="0">
       <text>
         <t>ShareBasedCompensationArrangementByShareBasedPaymentAwardEquityInstrumentsOtherThanOptionsVestedInPeriod @ FY2022; raw=389,000</t>
       </text>
@@ -6446,7 +6446,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mnst:CocaColaEuropeanPartnersMember</t>
+          <t xml:space="preserve">  Coca-Cola European Partners (CCEP)</t>
         </is>
       </c>
       <c r="B40" s="9" t="n">
@@ -6528,7 +6528,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mnst:CocaColaConsolidatedIncMember</t>
+          <t xml:space="preserve">  Coca-Cola Consolidated, Inc.</t>
         </is>
       </c>
       <c r="B41" s="9" t="n">
@@ -6607,7 +6607,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mnst:CocaColaCompanyMember</t>
+          <t xml:space="preserve">  Coca-Cola Company</t>
         </is>
       </c>
       <c r="B42" s="9" t="n">
@@ -6656,7 +6656,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mnst:ReyesCocaColaBottlingMember</t>
+          <t xml:space="preserve">  Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="B43" s="9" t="n">
@@ -6717,7 +6717,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mnst:ReyesHoldingsLlcMember</t>
+          <t xml:space="preserve">  Reyes Holdings LLC</t>
         </is>
       </c>
       <c r="N44" s="9" t="n">
@@ -6757,7 +6757,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mnst:ReyesCocaColaBottlingLlcMember</t>
+          <t xml:space="preserve">  Reyes Coca-Cola Bottling LLC</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
+          <t>Q4 2022</t>
+        </is>
+      </c>
+      <c r="P65" s="5" t="inlineStr">
+        <is>
           <t>FY2022</t>
-        </is>
-      </c>
-      <c r="P65" s="5" t="inlineStr">
-        <is>
-          <t>Q4 2022</t>
         </is>
       </c>
       <c r="Q65" s="5" t="inlineStr">
@@ -7070,7 +7070,7 @@
       <c r="K67" s="8" t="n">
         <v>60600</v>
       </c>
-      <c r="O67" s="8" t="n">
+      <c r="P67" s="8" t="n">
         <v>54000</v>
       </c>
       <c r="U67" s="8" t="n">
@@ -7111,7 +7111,7 @@
       <c r="K69" s="8" t="n">
         <v>8300.000000000002</v>
       </c>
-      <c r="O69" s="8" t="n">
+      <c r="P69" s="8" t="n">
         <v>9400</v>
       </c>
       <c r="U69" s="8" t="n">
@@ -7136,7 +7136,7 @@
       <c r="K70" s="8" t="n">
         <v>1600</v>
       </c>
-      <c r="O70" s="8" t="n">
+      <c r="P70" s="8" t="n">
         <v>700</v>
       </c>
       <c r="U70" s="8" t="n">
@@ -7263,10 +7263,10 @@
         <v>95.17</v>
       </c>
       <c r="O74" s="10" t="n">
+        <v>90.29000000000001</v>
+      </c>
+      <c r="P74" s="10" t="n">
         <v>74.26000000000001</v>
-      </c>
-      <c r="P74" s="10" t="n">
-        <v>90.29000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -7278,7 +7278,7 @@
       <c r="K75" s="10" t="n">
         <v>44.56</v>
       </c>
-      <c r="O75" s="10" t="n">
+      <c r="P75" s="10" t="n">
         <v>37.13</v>
       </c>
       <c r="R75" s="10" t="n">
@@ -7410,7 +7410,7 @@
       <c r="N79" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="P79" s="8" t="n">
+      <c r="O79" s="8" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       <c r="K83" s="8" t="n">
         <v>344000</v>
       </c>
-      <c r="O83" s="8" t="n">
+      <c r="P83" s="8" t="n">
         <v>389000</v>
       </c>
     </row>
